--- a/data/trans_dic/P23_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P23_R-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,64; 48,09</t>
+          <t>35,28; 47,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>40,32; 52,42</t>
+          <t>39,76; 52,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,36; 42,25</t>
+          <t>31,13; 42,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,15; 33,71</t>
+          <t>22,77; 33,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,46; 41,13</t>
+          <t>28,41; 40,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,08; 31,66</t>
+          <t>21,05; 30,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,86; 39,23</t>
+          <t>30,53; 38,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,08; 44,65</t>
+          <t>35,87; 44,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,46; 34,97</t>
+          <t>27,56; 35,49</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,6; 43,76</t>
+          <t>34,71; 43,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,22; 46,13</t>
+          <t>36,24; 45,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,51; 46,66</t>
+          <t>36,75; 46,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,12; 27,56</t>
+          <t>19,87; 27,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,85; 33,14</t>
+          <t>25,14; 33,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,29; 31,68</t>
+          <t>23,35; 31,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,12; 34,23</t>
+          <t>27,88; 34,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,99; 38,47</t>
+          <t>31,88; 37,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,46; 37,77</t>
+          <t>31,5; 37,41</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,15; 52,32</t>
+          <t>40,11; 51,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,94; 44,52</t>
+          <t>34,2; 45,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,3; 35,14</t>
+          <t>25,69; 35,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,88; 33,7</t>
+          <t>23,44; 33,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,27; 31,3</t>
+          <t>21,35; 31,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,01; 29,41</t>
+          <t>19,92; 29,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,17; 40,91</t>
+          <t>33,2; 41,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,44; 35,95</t>
+          <t>28,71; 36,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23,78; 30,49</t>
+          <t>23,99; 30,73</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,53; 53,06</t>
+          <t>42,3; 52,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,01; 40,64</t>
+          <t>30,81; 41,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,63; 43,91</t>
+          <t>33,64; 43,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,8; 32,93</t>
+          <t>23,75; 32,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,45; 31,65</t>
+          <t>22,52; 31,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,33; 33,23</t>
+          <t>23,83; 33,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,44; 41,48</t>
+          <t>34,24; 41,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,8; 34,67</t>
+          <t>27,82; 34,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,76; 36,88</t>
+          <t>29,54; 36,75</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>33,89; 48,2</t>
+          <t>34,43; 48,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36,22; 50,67</t>
+          <t>35,74; 49,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34,2; 48,27</t>
+          <t>33,53; 46,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,9; 35,69</t>
+          <t>22,89; 35,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,74; 36,85</t>
+          <t>23,79; 36,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,61; 32,33</t>
+          <t>20,53; 31,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,36; 40,05</t>
+          <t>30,23; 39,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>32,08; 41,67</t>
+          <t>31,6; 40,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,02; 37,99</t>
+          <t>28,73; 37,97</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40,76; 53,16</t>
+          <t>40,53; 51,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25,18; 36,86</t>
+          <t>24,88; 36,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28,38; 40,25</t>
+          <t>28,45; 40,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,88; 28,76</t>
+          <t>19,13; 29,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,24; 29,55</t>
+          <t>19,34; 29,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,38; 31,89</t>
+          <t>21,64; 32,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,85; 38,76</t>
+          <t>31,08; 38,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,61; 30,83</t>
+          <t>23,44; 31,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,47; 34,2</t>
+          <t>26,71; 34,07</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>34,4; 41,95</t>
+          <t>34,07; 42,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38,32; 46,21</t>
+          <t>38,08; 46,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,1; 34,44</t>
+          <t>27,07; 34,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21,84; 28,47</t>
+          <t>21,87; 28,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,74; 32,07</t>
+          <t>24,72; 31,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,96; 28,98</t>
+          <t>22,12; 29,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,05; 34,24</t>
+          <t>28,82; 34,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>32,4; 37,84</t>
+          <t>32,38; 37,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,5; 30,68</t>
+          <t>25,61; 30,58</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>39,18; 46,27</t>
+          <t>39,15; 46,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>34,59; 41,68</t>
+          <t>34,72; 41,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29,49; 36,71</t>
+          <t>29,37; 36,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20,65; 27,14</t>
+          <t>20,97; 27,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,51; 28,73</t>
+          <t>22,79; 28,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,93; 29,23</t>
+          <t>22,89; 28,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,52; 35,39</t>
+          <t>30,51; 35,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>29,31; 34,03</t>
+          <t>29,03; 33,88</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>27,2; 31,9</t>
+          <t>26,92; 31,57</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>40,46; 44,04</t>
+          <t>40,59; 44,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>37,86; 41,33</t>
+          <t>37,88; 41,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33,41; 36,82</t>
+          <t>33,38; 36,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24,11; 27,19</t>
+          <t>24,15; 26,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>25,88; 28,93</t>
+          <t>25,92; 28,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,68; 27,64</t>
+          <t>24,63; 27,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,61; 34,98</t>
+          <t>32,56; 35,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>32,16; 34,63</t>
+          <t>32,26; 34,57</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29,29; 31,62</t>
+          <t>29,32; 31,6</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>97310; 131292</t>
+          <t>96316; 128414</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>118851; 154504</t>
+          <t>117194; 153386</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89188; 124119</t>
+          <t>91451; 125764</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57785; 87924</t>
+          <t>59384; 87449</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>81742; 118134</t>
+          <t>81620; 115982</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60864; 91416</t>
+          <t>60767; 88898</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>164736; 209448</t>
+          <t>162977; 207146</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>209983; 259882</t>
+          <t>208731; 259682</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>159955; 203688</t>
+          <t>160529; 206723</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>170232; 215299</t>
+          <t>170777; 214858</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>188150; 233188</t>
+          <t>183201; 232354</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>188202; 234075</t>
+          <t>184401; 231193</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>101390; 138880</t>
+          <t>100114; 138589</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>130167; 173579</t>
+          <t>131693; 174565</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>121304; 165004</t>
+          <t>121605; 164370</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>280057; 340943</t>
+          <t>277674; 339186</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>329260; 395929</t>
+          <t>328150; 391029</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>321679; 386255</t>
+          <t>322146; 382549</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>131192; 166810</t>
+          <t>127891; 165238</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>109970; 144279</t>
+          <t>110828; 146552</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80584; 111956</t>
+          <t>81827; 113817</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>80097; 113030</t>
+          <t>78636; 111045</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>72333; 106431</t>
+          <t>72597; 105506</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67302; 98919</t>
+          <t>66983; 98032</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>217039; 267638</t>
+          <t>217217; 268323</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>188874; 238707</t>
+          <t>190654; 239508</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>155752; 199656</t>
+          <t>157093; 201232</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>152527; 190305</t>
+          <t>151701; 189434</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>112214; 151987</t>
+          <t>115229; 154895</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>124411; 162451</t>
+          <t>124447; 162638</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>88395; 122324</t>
+          <t>88224; 122388</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>87304; 123086</t>
+          <t>87587; 123202</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>90068; 128282</t>
+          <t>91976; 127693</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>251443; 302825</t>
+          <t>249999; 301631</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>212110; 264525</t>
+          <t>212276; 265359</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>224958; 278803</t>
+          <t>223284; 277806</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>68899; 97989</t>
+          <t>69990; 98762</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>77011; 107723</t>
+          <t>75999; 105888</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72236; 101956</t>
+          <t>70823; 99066</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47563; 74107</t>
+          <t>47538; 74550</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>52121; 80921</t>
+          <t>52235; 79231</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>45045; 70679</t>
+          <t>44876; 69422</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>124773; 164600</t>
+          <t>124221; 162884</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>138651; 180083</t>
+          <t>136593; 176248</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>124749; 163283</t>
+          <t>123482; 163188</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>110384; 143950</t>
+          <t>109768; 140783</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>68981; 100978</t>
+          <t>68180; 99270</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>74686; 105899</t>
+          <t>74857; 105798</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>52515; 79992</t>
+          <t>53205; 81218</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>53888; 82745</t>
+          <t>54146; 82596</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>58397; 87098</t>
+          <t>59102; 89195</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>169337; 212765</t>
+          <t>170612; 213940</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>130824; 170817</t>
+          <t>129850; 172449</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>141938; 183393</t>
+          <t>143222; 182708</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>211567; 258034</t>
+          <t>209558; 260404</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>253972; 306263</t>
+          <t>252360; 306468</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>177639; 225740</t>
+          <t>177437; 227392</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>139384; 181712</t>
+          <t>139565; 183821</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>171643; 222521</t>
+          <t>171515; 219930</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>151378; 199805</t>
+          <t>152448; 199947</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>364088; 429141</t>
+          <t>361195; 430152</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>439566; 513292</t>
+          <t>439278; 509504</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>342875; 412632</t>
+          <t>344381; 411298</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>291437; 344170</t>
+          <t>291198; 343872</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>269138; 324280</t>
+          <t>270123; 325363</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>229606; 285832</t>
+          <t>228677; 284051</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>161761; 212613</t>
+          <t>164333; 211739</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>185211; 236367</t>
+          <t>187555; 237238</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>189432; 241509</t>
+          <t>189123; 239010</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>466065; 540526</t>
+          <t>465979; 541106</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>469305; 544732</t>
+          <t>464760; 542350</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>436427; 511861</t>
+          <t>432061; 506546</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1325414; 1442511</t>
+          <t>1329366; 1446641</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1296941; 1415781</t>
+          <t>1297780; 1415261</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1133536; 1249039</t>
+          <t>1132509; 1247052</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>814610; 918767</t>
+          <t>815961; 910974</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>920492; 1029014</t>
+          <t>921956; 1029669</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>873361; 978159</t>
+          <t>871670; 977404</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2170312; 2328069</t>
+          <t>2166858; 2330261</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2245409; 2417827</t>
+          <t>2252453; 2413925</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2029989; 2191972</t>
+          <t>2032585; 2190225</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P23_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P23_R-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,28; 47,04</t>
+          <t>35,09; 47,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39,76; 52,04</t>
+          <t>40,43; 52,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,13; 42,81</t>
+          <t>31,53; 43,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,77; 33,53</t>
+          <t>22,29; 34,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,41; 40,38</t>
+          <t>28,29; 40,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,05; 30,79</t>
+          <t>20,55; 30,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,53; 38,8</t>
+          <t>30,91; 39,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,87; 44,62</t>
+          <t>36,23; 44,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,56; 35,49</t>
+          <t>27,49; 35,34</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,71; 43,67</t>
+          <t>34,37; 43,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,24; 45,96</t>
+          <t>37,11; 46,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,75; 46,08</t>
+          <t>37,52; 46,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,87; 27,5</t>
+          <t>20,05; 27,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,14; 33,33</t>
+          <t>24,85; 32,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,35; 31,56</t>
+          <t>23,5; 31,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,88; 34,06</t>
+          <t>28,37; 34,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,88; 37,99</t>
+          <t>31,2; 37,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,5; 37,41</t>
+          <t>31,37; 37,43</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40,11; 51,82</t>
+          <t>40,72; 51,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,2; 45,23</t>
+          <t>33,6; 44,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,69; 35,73</t>
+          <t>25,36; 35,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,44; 33,11</t>
+          <t>23,54; 33,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,35; 31,03</t>
+          <t>20,56; 30,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,92; 29,15</t>
+          <t>19,72; 29,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,2; 41,01</t>
+          <t>33,48; 40,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,71; 36,07</t>
+          <t>28,5; 36,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23,99; 30,73</t>
+          <t>23,75; 30,64</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,3; 52,82</t>
+          <t>42,24; 52,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,81; 41,42</t>
+          <t>30,17; 40,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,64; 43,96</t>
+          <t>33,49; 43,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,75; 32,95</t>
+          <t>23,93; 32,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,52; 31,68</t>
+          <t>22,65; 32,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,83; 33,08</t>
+          <t>23,83; 33,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,24; 41,31</t>
+          <t>34,41; 41,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,82; 34,78</t>
+          <t>27,82; 34,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,54; 36,75</t>
+          <t>29,62; 36,56</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,43; 48,58</t>
+          <t>34,96; 48,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35,74; 49,8</t>
+          <t>35,56; 50,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33,53; 46,9</t>
+          <t>34,09; 47,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,89; 35,9</t>
+          <t>22,59; 36,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,79; 36,08</t>
+          <t>23,82; 36,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,53; 31,76</t>
+          <t>21,06; 32,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,23; 39,63</t>
+          <t>29,82; 39,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>31,6; 40,78</t>
+          <t>31,65; 41,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,73; 37,97</t>
+          <t>28,97; 37,6</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40,53; 51,99</t>
+          <t>40,83; 52,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,88; 36,23</t>
+          <t>24,91; 36,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28,45; 40,21</t>
+          <t>27,86; 39,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,13; 29,2</t>
+          <t>18,77; 28,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,34; 29,5</t>
+          <t>19,22; 28,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,64; 32,66</t>
+          <t>21,47; 32,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,08; 38,97</t>
+          <t>30,99; 38,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,44; 31,13</t>
+          <t>23,32; 31,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,71; 34,07</t>
+          <t>26,33; 34,53</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>34,07; 42,34</t>
+          <t>34,22; 42,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38,08; 46,24</t>
+          <t>38,42; 46,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,07; 34,69</t>
+          <t>27,04; 34,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21,87; 28,8</t>
+          <t>21,85; 28,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,72; 31,7</t>
+          <t>24,76; 31,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,12; 29,01</t>
+          <t>22,31; 28,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,82; 34,32</t>
+          <t>29,09; 34,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>32,38; 37,56</t>
+          <t>32,38; 37,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,61; 30,58</t>
+          <t>25,53; 30,76</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>39,15; 46,23</t>
+          <t>39,21; 46,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>34,72; 41,82</t>
+          <t>34,62; 41,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29,37; 36,48</t>
+          <t>29,53; 36,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20,97; 27,02</t>
+          <t>20,84; 26,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,79; 28,83</t>
+          <t>22,1; 28,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,89; 28,93</t>
+          <t>22,9; 29,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,51; 35,43</t>
+          <t>30,43; 35,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>29,03; 33,88</t>
+          <t>29,25; 34,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>26,92; 31,57</t>
+          <t>27,07; 31,85</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>40,59; 44,17</t>
+          <t>40,64; 44,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>37,88; 41,31</t>
+          <t>37,85; 41,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33,38; 36,76</t>
+          <t>33,65; 36,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24,15; 26,96</t>
+          <t>24,13; 27,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>25,92; 28,95</t>
+          <t>25,88; 29,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,63; 27,62</t>
+          <t>24,63; 27,82</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,56; 35,02</t>
+          <t>32,66; 34,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>32,26; 34,57</t>
+          <t>32,27; 34,54</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29,32; 31,6</t>
+          <t>29,35; 31,64</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>96316; 128414</t>
+          <t>95803; 129604</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>117194; 153386</t>
+          <t>119166; 153841</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91451; 125764</t>
+          <t>92616; 128033</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>59384; 87449</t>
+          <t>58146; 89529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>81620; 115982</t>
+          <t>81262; 115655</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60767; 88898</t>
+          <t>59321; 89324</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>162977; 207146</t>
+          <t>165016; 208363</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>208731; 259682</t>
+          <t>210863; 259941</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>160529; 206723</t>
+          <t>160117; 205814</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>170777; 214858</t>
+          <t>169113; 214860</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>183201; 232354</t>
+          <t>187620; 235397</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>184401; 231193</t>
+          <t>188244; 232741</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100114; 138589</t>
+          <t>101059; 138707</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>131693; 174565</t>
+          <t>130178; 172547</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>121605; 164370</t>
+          <t>122407; 161765</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>277674; 339186</t>
+          <t>282604; 342018</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>328150; 391029</t>
+          <t>321109; 388223</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>322146; 382549</t>
+          <t>320755; 382720</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>127891; 165238</t>
+          <t>129821; 165614</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>110828; 146552</t>
+          <t>108866; 144140</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81827; 113817</t>
+          <t>80774; 111823</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>78636; 111045</t>
+          <t>78956; 111715</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>72597; 105506</t>
+          <t>69916; 103495</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>66983; 98032</t>
+          <t>66327; 98166</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>217217; 268323</t>
+          <t>219016; 267746</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>190654; 239508</t>
+          <t>189268; 240164</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>157093; 201232</t>
+          <t>155501; 200650</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>151701; 189434</t>
+          <t>151497; 189144</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>115229; 154895</t>
+          <t>112846; 149861</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>124447; 162638</t>
+          <t>123898; 160522</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>88224; 122388</t>
+          <t>88874; 120804</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>87587; 123202</t>
+          <t>88107; 125371</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>91976; 127693</t>
+          <t>91997; 128018</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>249999; 301631</t>
+          <t>251219; 301471</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>212276; 265359</t>
+          <t>212272; 262530</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>223284; 277806</t>
+          <t>223929; 276410</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>69990; 98762</t>
+          <t>71073; 98771</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>75999; 105888</t>
+          <t>75603; 107896</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70823; 99066</t>
+          <t>72004; 99513</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47538; 74550</t>
+          <t>46917; 74864</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>52235; 79231</t>
+          <t>52304; 79572</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44876; 69422</t>
+          <t>46029; 70083</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>124221; 162884</t>
+          <t>122544; 163694</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>136593; 176248</t>
+          <t>136775; 179139</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>123482; 163188</t>
+          <t>124515; 161620</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>109768; 140783</t>
+          <t>110581; 141426</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>68180; 99270</t>
+          <t>68257; 99518</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>74857; 105798</t>
+          <t>73296; 103939</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53205; 81218</t>
+          <t>52206; 79207</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>54146; 82596</t>
+          <t>53824; 80585</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>59102; 89195</t>
+          <t>58641; 88668</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>170612; 213940</t>
+          <t>170103; 211841</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>129850; 172449</t>
+          <t>129219; 171874</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>143222; 182708</t>
+          <t>141198; 185141</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>209558; 260404</t>
+          <t>210432; 259116</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>252360; 306468</t>
+          <t>254661; 309869</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>177437; 227392</t>
+          <t>177233; 226674</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>139565; 183821</t>
+          <t>139459; 184869</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>171515; 219930</t>
+          <t>171807; 219680</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>152448; 199947</t>
+          <t>153817; 198482</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>361195; 430152</t>
+          <t>364547; 429546</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>439278; 509504</t>
+          <t>439340; 511071</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>344381; 411298</t>
+          <t>343365; 413687</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>291198; 343872</t>
+          <t>291646; 345328</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>270123; 325363</t>
+          <t>269361; 323817</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>228677; 284051</t>
+          <t>229891; 285416</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>164333; 211739</t>
+          <t>163321; 210281</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>187555; 237238</t>
+          <t>181858; 236942</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>189123; 239010</t>
+          <t>189186; 243262</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>465979; 541106</t>
+          <t>464724; 539888</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>464760; 542350</t>
+          <t>468297; 546756</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>432061; 506546</t>
+          <t>434405; 511045</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1329366; 1446641</t>
+          <t>1331274; 1442553</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1297780; 1415261</t>
+          <t>1296778; 1414730</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1132509; 1247052</t>
+          <t>1141425; 1252088</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>815961; 910974</t>
+          <t>815438; 919173</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>921956; 1029669</t>
+          <t>920335; 1033648</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>871670; 977404</t>
+          <t>871656; 984620</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2166858; 2330261</t>
+          <t>2173732; 2325182</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2252453; 2413925</t>
+          <t>2253291; 2411864</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2032585; 2190225</t>
+          <t>2034452; 2193205</t>
         </is>
       </c>
     </row>
